--- a/tmp/report-export-check.xlsx
+++ b/tmp/report-export-check.xlsx
@@ -37,6 +37,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.##&quot;%&quot;"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -69,11 +72,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -146,7 +151,7 @@
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
     </row>
@@ -245,14 +250,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">دليل المزودين</t>
+          <t xml:space="preserve">دليل المزودين · 5</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"> • 5 سجل</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -451,14 +456,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">المخزون</t>
+          <t xml:space="preserve">المخزون · 8</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">لقطة المخزون الحالية عند إنشاء التقرير؛ لا تمثل رصيدًا تاريخيًا عند نهاية الفترة. • 8 سجل</t>
+          <t xml:space="preserve">لقطة المخزون الحالية عند إنشاء التقرير؛ لا تمثل رصيدًا تاريخيًا عند نهاية الفترة.</t>
         </is>
       </c>
     </row>
@@ -557,7 +562,7 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
@@ -565,31 +570,31 @@
           <t xml:space="preserve">2027-12-31</t>
         </is>
       </c>
-      <c r="F4" s="0">
+      <c r="F4" s="2">
         <v>24</v>
       </c>
-      <c r="G4" s="0">
+      <c r="G4" s="2">
         <v>24</v>
       </c>
-      <c r="H4" s="0">
-        <v>0</v>
-      </c>
-      <c r="I4" s="0">
-        <v>0</v>
-      </c>
-      <c r="J4" s="0">
-        <v>0</v>
-      </c>
-      <c r="K4" s="0">
-        <v>0</v>
-      </c>
-      <c r="L4" s="0">
-        <v>0</v>
-      </c>
-      <c r="M4" s="0">
-        <v>0</v>
-      </c>
-      <c r="N4" s="0">
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
         <v>105600</v>
       </c>
       <c r="O4" s="0" t="inlineStr">
@@ -616,7 +621,7 @@
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -624,31 +629,31 @@
           <t xml:space="preserve">2027-12-31</t>
         </is>
       </c>
-      <c r="F5" s="0">
+      <c r="F5" s="2">
         <v>24</v>
       </c>
-      <c r="G5" s="0">
+      <c r="G5" s="2">
         <v>24</v>
       </c>
-      <c r="H5" s="0">
-        <v>0</v>
-      </c>
-      <c r="I5" s="0">
-        <v>0</v>
-      </c>
-      <c r="J5" s="0">
-        <v>0</v>
-      </c>
-      <c r="K5" s="0">
-        <v>0</v>
-      </c>
-      <c r="L5" s="0">
-        <v>0</v>
-      </c>
-      <c r="M5" s="0">
-        <v>0</v>
-      </c>
-      <c r="N5" s="0">
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2">
         <v>213600</v>
       </c>
       <c r="O5" s="0" t="inlineStr">
@@ -675,7 +680,7 @@
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
@@ -683,31 +688,31 @@
           <t xml:space="preserve">2026-10-12</t>
         </is>
       </c>
-      <c r="F6" s="0">
+      <c r="F6" s="2">
         <v>24</v>
       </c>
-      <c r="G6" s="0">
+      <c r="G6" s="2">
         <v>24</v>
       </c>
-      <c r="H6" s="0">
-        <v>0</v>
-      </c>
-      <c r="I6" s="0">
-        <v>0</v>
-      </c>
-      <c r="J6" s="0">
-        <v>0</v>
-      </c>
-      <c r="K6" s="0">
-        <v>0</v>
-      </c>
-      <c r="L6" s="0">
-        <v>0</v>
-      </c>
-      <c r="M6" s="0">
-        <v>0</v>
-      </c>
-      <c r="N6" s="0">
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
         <v>105600</v>
       </c>
       <c r="O6" s="0" t="inlineStr">
@@ -734,7 +739,7 @@
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
@@ -742,31 +747,31 @@
           <t xml:space="preserve">2027-12-31</t>
         </is>
       </c>
-      <c r="F7" s="0">
+      <c r="F7" s="2">
         <v>24</v>
       </c>
-      <c r="G7" s="0">
+      <c r="G7" s="2">
         <v>24</v>
       </c>
-      <c r="H7" s="0">
-        <v>0</v>
-      </c>
-      <c r="I7" s="0">
-        <v>0</v>
-      </c>
-      <c r="J7" s="0">
-        <v>0</v>
-      </c>
-      <c r="K7" s="0">
-        <v>0</v>
-      </c>
-      <c r="L7" s="0">
-        <v>0</v>
-      </c>
-      <c r="M7" s="0">
-        <v>0</v>
-      </c>
-      <c r="N7" s="0">
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
         <v>345600</v>
       </c>
       <c r="O7" s="0" t="inlineStr">
@@ -793,7 +798,7 @@
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
@@ -801,31 +806,31 @@
           <t xml:space="preserve">2027-12-31</t>
         </is>
       </c>
-      <c r="F8" s="0">
+      <c r="F8" s="2">
         <v>24</v>
       </c>
-      <c r="G8" s="0">
+      <c r="G8" s="2">
         <v>24</v>
       </c>
-      <c r="H8" s="0">
-        <v>0</v>
-      </c>
-      <c r="I8" s="0">
-        <v>0</v>
-      </c>
-      <c r="J8" s="0">
-        <v>0</v>
-      </c>
-      <c r="K8" s="0">
-        <v>0</v>
-      </c>
-      <c r="L8" s="0">
-        <v>0</v>
-      </c>
-      <c r="M8" s="0">
-        <v>0</v>
-      </c>
-      <c r="N8" s="0">
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2">
         <v>105600</v>
       </c>
       <c r="O8" s="0" t="inlineStr">
@@ -852,7 +857,7 @@
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
@@ -860,31 +865,31 @@
           <t xml:space="preserve">2027-12-31</t>
         </is>
       </c>
-      <c r="F9" s="0">
+      <c r="F9" s="2">
         <v>24</v>
       </c>
-      <c r="G9" s="0">
+      <c r="G9" s="2">
         <v>24</v>
       </c>
-      <c r="H9" s="0">
-        <v>0</v>
-      </c>
-      <c r="I9" s="0">
-        <v>0</v>
-      </c>
-      <c r="J9" s="0">
-        <v>0</v>
-      </c>
-      <c r="K9" s="0">
-        <v>0</v>
-      </c>
-      <c r="L9" s="0">
-        <v>0</v>
-      </c>
-      <c r="M9" s="0">
-        <v>0</v>
-      </c>
-      <c r="N9" s="0">
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2">
         <v>213600</v>
       </c>
       <c r="O9" s="0" t="inlineStr">
@@ -911,7 +916,7 @@
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="E10" s="0" t="inlineStr">
@@ -919,31 +924,31 @@
           <t xml:space="preserve">2026-10-12</t>
         </is>
       </c>
-      <c r="F10" s="0">
+      <c r="F10" s="2">
         <v>24</v>
       </c>
-      <c r="G10" s="0">
+      <c r="G10" s="2">
         <v>24</v>
       </c>
-      <c r="H10" s="0">
-        <v>0</v>
-      </c>
-      <c r="I10" s="0">
-        <v>0</v>
-      </c>
-      <c r="J10" s="0">
-        <v>0</v>
-      </c>
-      <c r="K10" s="0">
-        <v>0</v>
-      </c>
-      <c r="L10" s="0">
-        <v>0</v>
-      </c>
-      <c r="M10" s="0">
-        <v>0</v>
-      </c>
-      <c r="N10" s="0">
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2">
         <v>105600</v>
       </c>
       <c r="O10" s="0" t="inlineStr">
@@ -970,7 +975,7 @@
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="E11" s="0" t="inlineStr">
@@ -978,31 +983,31 @@
           <t xml:space="preserve">2027-12-31</t>
         </is>
       </c>
-      <c r="F11" s="0">
+      <c r="F11" s="2">
         <v>24</v>
       </c>
-      <c r="G11" s="0">
+      <c r="G11" s="2">
         <v>24</v>
       </c>
-      <c r="H11" s="0">
-        <v>0</v>
-      </c>
-      <c r="I11" s="0">
-        <v>0</v>
-      </c>
-      <c r="J11" s="0">
-        <v>0</v>
-      </c>
-      <c r="K11" s="0">
-        <v>0</v>
-      </c>
-      <c r="L11" s="0">
-        <v>0</v>
-      </c>
-      <c r="M11" s="0">
-        <v>0</v>
-      </c>
-      <c r="N11" s="0">
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2">
         <v>345600</v>
       </c>
       <c r="O11" s="0" t="inlineStr">
@@ -1037,14 +1042,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">أرصدة المحافظ حسب الخدمة</t>
+          <t xml:space="preserve">أرصدة المحافظ حسب الخدمة · 18</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"> • 18 سجل</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -1106,19 +1111,19 @@
           <t xml:space="preserve">البطاقات — رصيد تشغيلي</t>
         </is>
       </c>
-      <c r="D4" s="0">
-        <v>0</v>
-      </c>
-      <c r="E4" s="0">
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
         <v>770400</v>
       </c>
-      <c r="F4" s="0">
-        <v>0</v>
-      </c>
-      <c r="G4" s="0">
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
         <v>770400</v>
       </c>
-      <c r="H4" s="0">
+      <c r="H4" s="2">
         <v>770400</v>
       </c>
     </row>
@@ -1138,19 +1143,19 @@
           <t xml:space="preserve">التعبئة المباشرة</t>
         </is>
       </c>
-      <c r="D5" s="0">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0">
-        <v>0</v>
-      </c>
-      <c r="F5" s="0">
-        <v>0</v>
-      </c>
-      <c r="G5" s="0">
-        <v>0</v>
-      </c>
-      <c r="H5" s="0">
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1170,19 +1175,19 @@
           <t xml:space="preserve">النقد والتعويضات</t>
         </is>
       </c>
-      <c r="D6" s="0">
-        <v>0</v>
-      </c>
-      <c r="E6" s="0">
-        <v>0</v>
-      </c>
-      <c r="F6" s="0">
-        <v>0</v>
-      </c>
-      <c r="G6" s="0">
-        <v>0</v>
-      </c>
-      <c r="H6" s="0">
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1202,19 +1207,19 @@
           <t xml:space="preserve">البطاقات — رصيد تشغيلي</t>
         </is>
       </c>
-      <c r="D7" s="0">
-        <v>0</v>
-      </c>
-      <c r="E7" s="0">
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
         <v>770400</v>
       </c>
-      <c r="F7" s="0">
-        <v>0</v>
-      </c>
-      <c r="G7" s="0">
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
         <v>770400</v>
       </c>
-      <c r="H7" s="0">
+      <c r="H7" s="2">
         <v>770400</v>
       </c>
     </row>
@@ -1234,19 +1239,19 @@
           <t xml:space="preserve">التعبئة المباشرة</t>
         </is>
       </c>
-      <c r="D8" s="0">
-        <v>0</v>
-      </c>
-      <c r="E8" s="0">
-        <v>0</v>
-      </c>
-      <c r="F8" s="0">
-        <v>0</v>
-      </c>
-      <c r="G8" s="0">
-        <v>0</v>
-      </c>
-      <c r="H8" s="0">
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1266,19 +1271,19 @@
           <t xml:space="preserve">النقد والتعويضات</t>
         </is>
       </c>
-      <c r="D9" s="0">
-        <v>0</v>
-      </c>
-      <c r="E9" s="0">
-        <v>0</v>
-      </c>
-      <c r="F9" s="0">
-        <v>0</v>
-      </c>
-      <c r="G9" s="0">
-        <v>0</v>
-      </c>
-      <c r="H9" s="0">
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1298,19 +1303,19 @@
           <t xml:space="preserve">البطاقات — رصيد تشغيلي</t>
         </is>
       </c>
-      <c r="D10" s="0">
-        <v>0</v>
-      </c>
-      <c r="E10" s="0">
-        <v>0</v>
-      </c>
-      <c r="F10" s="0">
-        <v>0</v>
-      </c>
-      <c r="G10" s="0">
-        <v>0</v>
-      </c>
-      <c r="H10" s="0">
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1330,19 +1335,19 @@
           <t xml:space="preserve">التعبئة المباشرة</t>
         </is>
       </c>
-      <c r="D11" s="0">
-        <v>0</v>
-      </c>
-      <c r="E11" s="0">
-        <v>0</v>
-      </c>
-      <c r="F11" s="0">
-        <v>0</v>
-      </c>
-      <c r="G11" s="0">
-        <v>0</v>
-      </c>
-      <c r="H11" s="0">
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1362,19 +1367,19 @@
           <t xml:space="preserve">النقد والتعويضات</t>
         </is>
       </c>
-      <c r="D12" s="0">
-        <v>0</v>
-      </c>
-      <c r="E12" s="0">
-        <v>0</v>
-      </c>
-      <c r="F12" s="0">
-        <v>0</v>
-      </c>
-      <c r="G12" s="0">
-        <v>0</v>
-      </c>
-      <c r="H12" s="0">
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1394,19 +1399,19 @@
           <t xml:space="preserve">البطاقات — رصيد تشغيلي</t>
         </is>
       </c>
-      <c r="D13" s="0">
-        <v>0</v>
-      </c>
-      <c r="E13" s="0">
-        <v>0</v>
-      </c>
-      <c r="F13" s="0">
-        <v>0</v>
-      </c>
-      <c r="G13" s="0">
-        <v>0</v>
-      </c>
-      <c r="H13" s="0">
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1426,19 +1431,19 @@
           <t xml:space="preserve">التعبئة المباشرة</t>
         </is>
       </c>
-      <c r="D14" s="0">
-        <v>0</v>
-      </c>
-      <c r="E14" s="0">
-        <v>0</v>
-      </c>
-      <c r="F14" s="0">
-        <v>0</v>
-      </c>
-      <c r="G14" s="0">
-        <v>0</v>
-      </c>
-      <c r="H14" s="0">
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1458,19 +1463,19 @@
           <t xml:space="preserve">النقد والتعويضات</t>
         </is>
       </c>
-      <c r="D15" s="0">
-        <v>0</v>
-      </c>
-      <c r="E15" s="0">
-        <v>0</v>
-      </c>
-      <c r="F15" s="0">
-        <v>0</v>
-      </c>
-      <c r="G15" s="0">
-        <v>0</v>
-      </c>
-      <c r="H15" s="0">
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1490,19 +1495,19 @@
           <t xml:space="preserve">البطاقات — رصيد تشغيلي</t>
         </is>
       </c>
-      <c r="D16" s="0">
-        <v>0</v>
-      </c>
-      <c r="E16" s="0">
-        <v>0</v>
-      </c>
-      <c r="F16" s="0">
-        <v>0</v>
-      </c>
-      <c r="G16" s="0">
-        <v>0</v>
-      </c>
-      <c r="H16" s="0">
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1522,19 +1527,19 @@
           <t xml:space="preserve">التعبئة المباشرة</t>
         </is>
       </c>
-      <c r="D17" s="0">
-        <v>0</v>
-      </c>
-      <c r="E17" s="0">
-        <v>0</v>
-      </c>
-      <c r="F17" s="0">
-        <v>0</v>
-      </c>
-      <c r="G17" s="0">
-        <v>0</v>
-      </c>
-      <c r="H17" s="0">
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1554,19 +1559,19 @@
           <t xml:space="preserve">النقد والتعويضات</t>
         </is>
       </c>
-      <c r="D18" s="0">
-        <v>0</v>
-      </c>
-      <c r="E18" s="0">
-        <v>0</v>
-      </c>
-      <c r="F18" s="0">
-        <v>0</v>
-      </c>
-      <c r="G18" s="0">
-        <v>0</v>
-      </c>
-      <c r="H18" s="0">
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1586,19 +1591,19 @@
           <t xml:space="preserve">البطاقات — رصيد تشغيلي</t>
         </is>
       </c>
-      <c r="D19" s="0">
-        <v>0</v>
-      </c>
-      <c r="E19" s="0">
-        <v>0</v>
-      </c>
-      <c r="F19" s="0">
-        <v>0</v>
-      </c>
-      <c r="G19" s="0">
-        <v>0</v>
-      </c>
-      <c r="H19" s="0">
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1618,19 +1623,19 @@
           <t xml:space="preserve">التعبئة المباشرة</t>
         </is>
       </c>
-      <c r="D20" s="0">
-        <v>0</v>
-      </c>
-      <c r="E20" s="0">
-        <v>0</v>
-      </c>
-      <c r="F20" s="0">
-        <v>0</v>
-      </c>
-      <c r="G20" s="0">
-        <v>0</v>
-      </c>
-      <c r="H20" s="0">
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1650,19 +1655,19 @@
           <t xml:space="preserve">النقد والتعويضات</t>
         </is>
       </c>
-      <c r="D21" s="0">
-        <v>0</v>
-      </c>
-      <c r="E21" s="0">
-        <v>0</v>
-      </c>
-      <c r="F21" s="0">
-        <v>0</v>
-      </c>
-      <c r="G21" s="0">
-        <v>0</v>
-      </c>
-      <c r="H21" s="0">
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1691,14 +1696,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">حركات محافظ الخدمات</t>
+          <t xml:space="preserve">حركات محافظ الخدمات · 2</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"> • 2 سجل</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -1742,7 +1747,7 @@
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SL-6a223008-49f</t>
+          <t xml:space="preserve">SL-4e8feafe-d41</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
@@ -1752,7 +1757,7 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
@@ -1770,14 +1775,14 @@
           <t xml:space="preserve">رصيد افتتاحي من تكلفة المخزون المتبقي</t>
         </is>
       </c>
-      <c r="G4" s="0">
+      <c r="G4" s="2">
         <v>770400</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SL-20a2580e-429</t>
+          <t xml:space="preserve">SL-f3b1cb6e-d70</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
@@ -1787,7 +1792,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
@@ -1805,7 +1810,7 @@
           <t xml:space="preserve">رصيد افتتاحي من تكلفة المخزون المتبقي</t>
         </is>
       </c>
-      <c r="G5" s="0">
+      <c r="G5" s="2">
         <v>770400</v>
       </c>
     </row>
@@ -1830,14 +1835,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">الأرصدة النقدية السابقة</t>
+          <t xml:space="preserve">الأرصدة النقدية السابقة · 6</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"> • 6 سجل</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -1869,7 +1874,7 @@
           <t xml:space="preserve">وكالة بغداد المركزية</t>
         </is>
       </c>
-      <c r="C4" s="0">
+      <c r="C4" s="2">
         <v>2000000</v>
       </c>
     </row>
@@ -1884,7 +1889,7 @@
           <t xml:space="preserve">وكالة الفرات</t>
         </is>
       </c>
-      <c r="C5" s="0">
+      <c r="C5" s="2">
         <v>1500000</v>
       </c>
     </row>
@@ -1899,7 +1904,7 @@
           <t xml:space="preserve">توزيع الكرادة</t>
         </is>
       </c>
-      <c r="C6" s="0">
+      <c r="C6" s="2">
         <v>750000</v>
       </c>
     </row>
@@ -1914,7 +1919,7 @@
           <t xml:space="preserve">مركز النور للاتصالات</t>
         </is>
       </c>
-      <c r="C7" s="0">
+      <c r="C7" s="2">
         <v>350000</v>
       </c>
     </row>
@@ -1929,7 +1934,7 @@
           <t xml:space="preserve">مكتبة الرافدين</t>
         </is>
       </c>
-      <c r="C8" s="0">
+      <c r="C8" s="2">
         <v>500000</v>
       </c>
     </row>
@@ -1944,7 +1949,7 @@
           <t xml:space="preserve">اتصالات العشار</t>
         </is>
       </c>
-      <c r="C9" s="0">
+      <c r="C9" s="2">
         <v>250000</v>
       </c>
     </row>
@@ -1975,14 +1980,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">فواتير تحميل ماسال</t>
+          <t xml:space="preserve">فواتير تحميل ماسال · 0</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"> • 0 سجل</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -2057,14 +2062,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">شبكة الوكلاء</t>
+          <t xml:space="preserve">شبكة الوكلاء · 3</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">السجلات الحالية ضمن النطاق. • 3 سجل</t>
+          <t xml:space="preserve">السجلات الحالية ضمن النطاق.</t>
         </is>
       </c>
     </row>
@@ -2224,14 +2229,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">الأجهزة ونقاط البيع</t>
+          <t xml:space="preserve">الأجهزة ونقاط البيع · 3</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"> • 3 سجل</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -2333,7 +2338,7 @@
           <t xml:space="preserve">مفعل</t>
         </is>
       </c>
-      <c r="J4" s="0">
+      <c r="J4" s="2">
         <v>5</v>
       </c>
     </row>
@@ -2383,7 +2388,7 @@
           <t xml:space="preserve">مفعل</t>
         </is>
       </c>
-      <c r="J5" s="0">
+      <c r="J5" s="2">
         <v>5</v>
       </c>
     </row>
@@ -2433,7 +2438,7 @@
           <t xml:space="preserve">مفعل</t>
         </is>
       </c>
-      <c r="J6" s="0">
+      <c r="J6" s="2">
         <v>3</v>
       </c>
     </row>
@@ -2459,14 +2464,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">قائمة الأسعار الحالية</t>
+          <t xml:space="preserve">قائمة الأسعار الحالية · 12</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">الأسعار الحالية؛ لا تطبق عليها فترة البيع. • 12 سجل</t>
+          <t xml:space="preserve">الأسعار الحالية؛ لا تطبق عليها فترة البيع.</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2508,7 @@
           <t xml:space="preserve">زين • 5,000 دينار</t>
         </is>
       </c>
-      <c r="C4" s="0">
+      <c r="C4" s="2">
         <v>4750</v>
       </c>
       <c r="D4" s="0" t="inlineStr">
@@ -2523,7 +2528,7 @@
           <t xml:space="preserve">آسياسيل • 10,000 دينار</t>
         </is>
       </c>
-      <c r="C5" s="0">
+      <c r="C5" s="2">
         <v>9250</v>
       </c>
       <c r="D5" s="0" t="inlineStr">
@@ -2543,7 +2548,7 @@
           <t xml:space="preserve">كورك • 5,000 دينار</t>
         </is>
       </c>
-      <c r="C6" s="0">
+      <c r="C6" s="2">
         <v>4750</v>
       </c>
       <c r="D6" s="0" t="inlineStr">
@@ -2563,7 +2568,7 @@
           <t xml:space="preserve">PlayStation • $10</t>
         </is>
       </c>
-      <c r="C7" s="0">
+      <c r="C7" s="2">
         <v>14750</v>
       </c>
       <c r="D7" s="0" t="inlineStr">
@@ -2583,7 +2588,7 @@
           <t xml:space="preserve">زين • 5,000 دينار</t>
         </is>
       </c>
-      <c r="C8" s="0">
+      <c r="C8" s="2">
         <v>4750</v>
       </c>
       <c r="D8" s="0" t="inlineStr">
@@ -2603,7 +2608,7 @@
           <t xml:space="preserve">آسياسيل • 10,000 دينار</t>
         </is>
       </c>
-      <c r="C9" s="0">
+      <c r="C9" s="2">
         <v>9250</v>
       </c>
       <c r="D9" s="0" t="inlineStr">
@@ -2623,7 +2628,7 @@
           <t xml:space="preserve">كورك • 5,000 دينار</t>
         </is>
       </c>
-      <c r="C10" s="0">
+      <c r="C10" s="2">
         <v>4750</v>
       </c>
       <c r="D10" s="0" t="inlineStr">
@@ -2643,7 +2648,7 @@
           <t xml:space="preserve">PlayStation • $10</t>
         </is>
       </c>
-      <c r="C11" s="0">
+      <c r="C11" s="2">
         <v>14750</v>
       </c>
       <c r="D11" s="0" t="inlineStr">
@@ -2663,7 +2668,7 @@
           <t xml:space="preserve">زين • 5,000 دينار</t>
         </is>
       </c>
-      <c r="C12" s="0">
+      <c r="C12" s="2">
         <v>4750</v>
       </c>
       <c r="D12" s="0" t="inlineStr">
@@ -2683,7 +2688,7 @@
           <t xml:space="preserve">آسياسيل • 10,000 دينار</t>
         </is>
       </c>
-      <c r="C13" s="0">
+      <c r="C13" s="2">
         <v>9250</v>
       </c>
       <c r="D13" s="0" t="inlineStr">
@@ -2703,7 +2708,7 @@
           <t xml:space="preserve">كورك • 5,000 دينار</t>
         </is>
       </c>
-      <c r="C14" s="0">
+      <c r="C14" s="2">
         <v>4750</v>
       </c>
       <c r="D14" s="0" t="inlineStr">
@@ -2723,7 +2728,7 @@
           <t xml:space="preserve">PlayStation • $10</t>
         </is>
       </c>
-      <c r="C15" s="0">
+      <c r="C15" s="2">
         <v>14750</v>
       </c>
       <c r="D15" s="0" t="inlineStr">
@@ -2756,14 +2761,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">طلبات اعتماد الأسعار</t>
+          <t xml:space="preserve">طلبات اعتماد الأسعار · 0</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"> • 0 سجل</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -2831,14 +2836,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">سجل المبيعات التفصيلي</t>
+          <t xml:space="preserve">سجل المبيعات التفصيلي · 0</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ربح البيع منفصل عن ربح تحميل ماسال؛ السجلات التي لا تملك تكلفة تحميل موثقة تعرض دون ربح محسوب. • 0 سجل</t>
+          <t xml:space="preserve">ربح البيع منفصل عن ربح تحميل ماسال؛ السجلات التي لا تملك تكلفة تحميل موثقة تعرض دون ربح محسوب.</t>
         </is>
       </c>
     </row>
@@ -2947,14 +2952,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">المطالبات والتسويات</t>
+          <t xml:space="preserve">المطالبات والتسويات · 0</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"> • 0 سجل</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -3060,14 +3065,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">سجل تصدير البطاقات</t>
+          <t xml:space="preserve">سجل تصدير البطاقات · 0</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">لا يتضمن التقرير رموز PIN أو كلمات التشفير. • 0 سجل</t>
+          <t xml:space="preserve">لا يتضمن التقرير رموز PIN أو كلمات التشفير.</t>
         </is>
       </c>
     </row>
@@ -3134,14 +3139,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">الدعم الفني</t>
+          <t xml:space="preserve">الدعم الفني · 1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"> • 1 سجل</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -3195,7 +3200,7 @@
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -3223,7 +3228,7 @@
           <t xml:space="preserve">مفتوحة</t>
         </is>
       </c>
-      <c r="H4" s="0">
+      <c r="H4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3249,14 +3254,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">تفاصيل ردود الدعم</t>
+          <t xml:space="preserve">تفاصيل ردود الدعم · 0</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"> • 0 سجل</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -3310,14 +3315,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">الموظفون والصلاحيات الفعلية</t>
+          <t xml:space="preserve">الموظفون والصلاحيات الفعلية · 5</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"> • 5 سجل</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -3409,13 +3414,13 @@
           <t xml:space="preserve">وكالة بغداد المركزية، وكالة الفرات، توزيع الكرادة</t>
         </is>
       </c>
-      <c r="H4" s="0">
+      <c r="H4" s="2">
         <v>167</v>
       </c>
-      <c r="I4" s="0">
-        <v>0</v>
-      </c>
-      <c r="J4" s="0">
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3455,13 +3460,13 @@
           <t xml:space="preserve">وكالة بغداد المركزية، توزيع الكرادة</t>
         </is>
       </c>
-      <c r="H5" s="0">
+      <c r="H5" s="2">
         <v>108</v>
       </c>
-      <c r="I5" s="0">
-        <v>0</v>
-      </c>
-      <c r="J5" s="0">
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3501,13 +3506,13 @@
           <t xml:space="preserve">وكالة بغداد المركزية، توزيع الكرادة</t>
         </is>
       </c>
-      <c r="H6" s="0">
+      <c r="H6" s="2">
         <v>114</v>
       </c>
-      <c r="I6" s="0">
-        <v>0</v>
-      </c>
-      <c r="J6" s="0">
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3547,13 +3552,13 @@
           <t xml:space="preserve">توزيع الكرادة</t>
         </is>
       </c>
-      <c r="H7" s="0">
+      <c r="H7" s="2">
         <v>76</v>
       </c>
-      <c r="I7" s="0">
-        <v>0</v>
-      </c>
-      <c r="J7" s="0">
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3593,13 +3598,13 @@
           <t xml:space="preserve">توزيع الكرادة</t>
         </is>
       </c>
-      <c r="H8" s="0">
+      <c r="H8" s="2">
         <v>38</v>
       </c>
-      <c r="I8" s="0">
-        <v>0</v>
-      </c>
-      <c r="J8" s="0">
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3627,14 +3632,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">تفاصيل تخصيص صلاحيات الموظفين</t>
+          <t xml:space="preserve">تفاصيل تخصيص صلاحيات الموظفين · 0</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"> • 0 سجل</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -3694,14 +3699,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">سجل التدقيق</t>
+          <t xml:space="preserve">سجل التدقيق · 1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">يعرض سجل النشاط دون تضمين قيم الحقول الحساسة. • 1 سجل</t>
+          <t xml:space="preserve">يعرض سجل النشاط دون تضمين قيم الحقول الحساسة.</t>
         </is>
       </c>
     </row>
@@ -3740,12 +3745,12 @@
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOG-5a6f8f6b-62c</t>
+          <t xml:space="preserve">LOG-4bd15507-22e</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -3789,14 +3794,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">إعدادات التشغيل</t>
+          <t xml:space="preserve">إعدادات التشغيل · 11</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">إعدادات حالية وليست سجلًا تاريخيًا. • 11 سجل</t>
+          <t xml:space="preserve">إعدادات حالية وليست سجلًا تاريخيًا.</t>
         </is>
       </c>
     </row>
@@ -3966,14 +3971,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">إعدادات الربط</t>
+          <t xml:space="preserve">إعدادات الربط · 0</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"> • 0 سجل</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -4022,14 +4027,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">سجل الإشعارات</t>
+          <t xml:space="preserve">سجل الإشعارات · 2</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"> • 2 سجل</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -4063,12 +4068,12 @@
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">NT-c39c6c97-f83</t>
+          <t xml:space="preserve">NT-e4ef664a-78a</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -4090,12 +4095,12 @@
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">NT-0ed21ee8-671</t>
+          <t xml:space="preserve">NT-c2b5ab52-16c</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -4140,14 +4145,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">المبيعات حسب الفئة</t>
+          <t xml:space="preserve">المبيعات حسب الفئة · 0</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"> • 0 سجل</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -4219,14 +4224,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">أداء الوكلاء</t>
+          <t xml:space="preserve">أداء الوكلاء · 0</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"> • 0 سجل</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -4298,14 +4303,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">أداء نقاط البيع</t>
+          <t xml:space="preserve">أداء نقاط البيع · 0</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"> • 0 سجل</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -4375,14 +4380,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">سجل محاولات الطباعة</t>
+          <t xml:space="preserve">سجل محاولات الطباعة · 0</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">محاولات الطباعة للعمليات المطابقة لفترة البيع. • 0 سجل</t>
+          <t xml:space="preserve">محاولات الطباعة للعمليات المطابقة لفترة البيع.</t>
         </is>
       </c>
     </row>
@@ -4448,14 +4453,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">تفاصيل التوريد والطلبيات</t>
+          <t xml:space="preserve">تفاصيل التوريد والطلبيات · 8</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">حركات التحميل خلال الفترة المحددة؛ الدفعات الملغاة تظهر بحالتها دون اعتبارها شراءً صافيًا. • 8 سجل</t>
+          <t xml:space="preserve">حركات التحميل خلال الفترة المحددة؛ الدفعات الملغاة تظهر بحالتها دون اعتبارها شراءً صافيًا.</t>
         </is>
       </c>
     </row>
@@ -4529,7 +4534,7 @@
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -4552,19 +4557,19 @@
           <t xml:space="preserve">بغداد</t>
         </is>
       </c>
-      <c r="G4" s="0">
+      <c r="G4" s="2">
         <v>24</v>
       </c>
-      <c r="H4" s="0">
-        <v>0</v>
-      </c>
-      <c r="I4" s="0">
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
         <v>4400</v>
       </c>
-      <c r="J4" s="0">
-        <v>0</v>
-      </c>
-      <c r="K4" s="0">
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
         <v>105600</v>
       </c>
       <c r="L4" s="0" t="inlineStr">
@@ -4581,7 +4586,7 @@
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -4604,19 +4609,19 @@
           <t xml:space="preserve">بغداد</t>
         </is>
       </c>
-      <c r="G5" s="0">
+      <c r="G5" s="2">
         <v>24</v>
       </c>
-      <c r="H5" s="0">
-        <v>0</v>
-      </c>
-      <c r="I5" s="0">
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
         <v>8900</v>
       </c>
-      <c r="J5" s="0">
-        <v>0</v>
-      </c>
-      <c r="K5" s="0">
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2">
         <v>213600</v>
       </c>
       <c r="L5" s="0" t="inlineStr">
@@ -4633,7 +4638,7 @@
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -4656,19 +4661,19 @@
           <t xml:space="preserve">بغداد</t>
         </is>
       </c>
-      <c r="G6" s="0">
+      <c r="G6" s="2">
         <v>24</v>
       </c>
-      <c r="H6" s="0">
-        <v>0</v>
-      </c>
-      <c r="I6" s="0">
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
         <v>4400</v>
       </c>
-      <c r="J6" s="0">
-        <v>0</v>
-      </c>
-      <c r="K6" s="0">
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
         <v>105600</v>
       </c>
       <c r="L6" s="0" t="inlineStr">
@@ -4685,7 +4690,7 @@
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -4708,19 +4713,19 @@
           <t xml:space="preserve">بغداد</t>
         </is>
       </c>
-      <c r="G7" s="0">
+      <c r="G7" s="2">
         <v>24</v>
       </c>
-      <c r="H7" s="0">
-        <v>0</v>
-      </c>
-      <c r="I7" s="0">
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
         <v>14400</v>
       </c>
-      <c r="J7" s="0">
-        <v>0</v>
-      </c>
-      <c r="K7" s="0">
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
         <v>345600</v>
       </c>
       <c r="L7" s="0" t="inlineStr">
@@ -4737,7 +4742,7 @@
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -4760,19 +4765,19 @@
           <t xml:space="preserve">البصرة</t>
         </is>
       </c>
-      <c r="G8" s="0">
+      <c r="G8" s="2">
         <v>24</v>
       </c>
-      <c r="H8" s="0">
-        <v>0</v>
-      </c>
-      <c r="I8" s="0">
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
         <v>4400</v>
       </c>
-      <c r="J8" s="0">
-        <v>0</v>
-      </c>
-      <c r="K8" s="0">
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
         <v>105600</v>
       </c>
       <c r="L8" s="0" t="inlineStr">
@@ -4789,7 +4794,7 @@
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -4812,19 +4817,19 @@
           <t xml:space="preserve">البصرة</t>
         </is>
       </c>
-      <c r="G9" s="0">
+      <c r="G9" s="2">
         <v>24</v>
       </c>
-      <c r="H9" s="0">
-        <v>0</v>
-      </c>
-      <c r="I9" s="0">
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
         <v>8900</v>
       </c>
-      <c r="J9" s="0">
-        <v>0</v>
-      </c>
-      <c r="K9" s="0">
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
         <v>213600</v>
       </c>
       <c r="L9" s="0" t="inlineStr">
@@ -4841,7 +4846,7 @@
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
@@ -4864,19 +4869,19 @@
           <t xml:space="preserve">البصرة</t>
         </is>
       </c>
-      <c r="G10" s="0">
+      <c r="G10" s="2">
         <v>24</v>
       </c>
-      <c r="H10" s="0">
-        <v>0</v>
-      </c>
-      <c r="I10" s="0">
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
         <v>4400</v>
       </c>
-      <c r="J10" s="0">
-        <v>0</v>
-      </c>
-      <c r="K10" s="0">
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2">
         <v>105600</v>
       </c>
       <c r="L10" s="0" t="inlineStr">
@@ -4893,7 +4898,7 @@
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
@@ -4916,19 +4921,19 @@
           <t xml:space="preserve">البصرة</t>
         </is>
       </c>
-      <c r="G11" s="0">
+      <c r="G11" s="2">
         <v>24</v>
       </c>
-      <c r="H11" s="0">
-        <v>0</v>
-      </c>
-      <c r="I11" s="0">
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
         <v>14400</v>
       </c>
-      <c r="J11" s="0">
-        <v>0</v>
-      </c>
-      <c r="K11" s="0">
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2">
         <v>345600</v>
       </c>
       <c r="L11" s="0" t="inlineStr">
@@ -4965,14 +4970,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">تتبع البطاقات دون الرموز</t>
+          <t xml:space="preserve">تتبع البطاقات دون الرموز · 192</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">حالة البطاقات الحالية؛ رموز PIN وCVC مستبعدة دائمًا من التقارير. • 192 سجل</t>
+          <t xml:space="preserve">حالة البطاقات الحالية؛ رموز PIN وCVC مستبعدة دائمًا من التقارير.</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5061,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
@@ -5074,7 +5079,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J4" s="0">
+      <c r="J4" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -5106,7 +5111,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
@@ -5124,7 +5129,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J5" s="0">
+      <c r="J5" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -5156,7 +5161,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
@@ -5174,7 +5179,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J6" s="0">
+      <c r="J6" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -5206,7 +5211,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
@@ -5224,7 +5229,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J7" s="0">
+      <c r="J7" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -5256,7 +5261,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
@@ -5274,7 +5279,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J8" s="0">
+      <c r="J8" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -5306,7 +5311,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
@@ -5324,7 +5329,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J9" s="0">
+      <c r="J9" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -5356,7 +5361,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G10" s="0" t="inlineStr">
@@ -5374,7 +5379,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J10" s="0">
+      <c r="J10" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -5406,7 +5411,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G11" s="0" t="inlineStr">
@@ -5424,7 +5429,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J11" s="0">
+      <c r="J11" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -5456,7 +5461,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G12" s="0" t="inlineStr">
@@ -5474,7 +5479,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J12" s="0">
+      <c r="J12" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -5506,7 +5511,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G13" s="0" t="inlineStr">
@@ -5524,7 +5529,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J13" s="0">
+      <c r="J13" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -5556,7 +5561,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G14" s="0" t="inlineStr">
@@ -5574,7 +5579,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J14" s="0">
+      <c r="J14" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -5606,7 +5611,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G15" s="0" t="inlineStr">
@@ -5624,7 +5629,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J15" s="0">
+      <c r="J15" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -5656,7 +5661,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G16" s="0" t="inlineStr">
@@ -5674,7 +5679,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J16" s="0">
+      <c r="J16" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -5706,7 +5711,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G17" s="0" t="inlineStr">
@@ -5724,7 +5729,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J17" s="0">
+      <c r="J17" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -5756,7 +5761,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G18" s="0" t="inlineStr">
@@ -5774,7 +5779,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J18" s="0">
+      <c r="J18" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -5806,7 +5811,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G19" s="0" t="inlineStr">
@@ -5824,7 +5829,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J19" s="0">
+      <c r="J19" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -5856,7 +5861,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G20" s="0" t="inlineStr">
@@ -5874,7 +5879,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J20" s="0">
+      <c r="J20" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -5906,7 +5911,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G21" s="0" t="inlineStr">
@@ -5924,7 +5929,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J21" s="0">
+      <c r="J21" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -5956,7 +5961,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G22" s="0" t="inlineStr">
@@ -5974,7 +5979,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J22" s="0">
+      <c r="J22" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -6006,7 +6011,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G23" s="0" t="inlineStr">
@@ -6024,7 +6029,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J23" s="0">
+      <c r="J23" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -6056,7 +6061,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G24" s="0" t="inlineStr">
@@ -6074,7 +6079,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J24" s="0">
+      <c r="J24" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -6106,7 +6111,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G25" s="0" t="inlineStr">
@@ -6124,7 +6129,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J25" s="0">
+      <c r="J25" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -6156,7 +6161,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G26" s="0" t="inlineStr">
@@ -6174,7 +6179,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J26" s="0">
+      <c r="J26" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -6206,7 +6211,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G27" s="0" t="inlineStr">
@@ -6224,7 +6229,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J27" s="0">
+      <c r="J27" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -6256,7 +6261,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G28" s="0" t="inlineStr">
@@ -6274,7 +6279,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J28" s="0">
+      <c r="J28" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -6306,7 +6311,7 @@
       </c>
       <c r="F29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G29" s="0" t="inlineStr">
@@ -6324,7 +6329,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J29" s="0">
+      <c r="J29" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -6356,7 +6361,7 @@
       </c>
       <c r="F30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G30" s="0" t="inlineStr">
@@ -6374,7 +6379,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J30" s="0">
+      <c r="J30" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -6406,7 +6411,7 @@
       </c>
       <c r="F31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G31" s="0" t="inlineStr">
@@ -6424,7 +6429,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J31" s="0">
+      <c r="J31" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -6456,7 +6461,7 @@
       </c>
       <c r="F32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G32" s="0" t="inlineStr">
@@ -6474,7 +6479,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J32" s="0">
+      <c r="J32" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -6506,7 +6511,7 @@
       </c>
       <c r="F33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G33" s="0" t="inlineStr">
@@ -6524,7 +6529,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J33" s="0">
+      <c r="J33" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -6556,7 +6561,7 @@
       </c>
       <c r="F34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G34" s="0" t="inlineStr">
@@ -6574,7 +6579,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J34" s="0">
+      <c r="J34" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -6606,7 +6611,7 @@
       </c>
       <c r="F35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G35" s="0" t="inlineStr">
@@ -6624,7 +6629,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J35" s="0">
+      <c r="J35" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -6656,7 +6661,7 @@
       </c>
       <c r="F36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G36" s="0" t="inlineStr">
@@ -6674,7 +6679,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J36" s="0">
+      <c r="J36" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -6706,7 +6711,7 @@
       </c>
       <c r="F37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G37" s="0" t="inlineStr">
@@ -6724,7 +6729,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J37" s="0">
+      <c r="J37" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -6756,7 +6761,7 @@
       </c>
       <c r="F38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G38" s="0" t="inlineStr">
@@ -6774,7 +6779,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J38" s="0">
+      <c r="J38" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -6806,7 +6811,7 @@
       </c>
       <c r="F39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G39" s="0" t="inlineStr">
@@ -6824,7 +6829,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J39" s="0">
+      <c r="J39" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -6856,7 +6861,7 @@
       </c>
       <c r="F40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G40" s="0" t="inlineStr">
@@ -6874,7 +6879,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J40" s="0">
+      <c r="J40" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -6906,7 +6911,7 @@
       </c>
       <c r="F41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G41" s="0" t="inlineStr">
@@ -6924,7 +6929,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J41" s="0">
+      <c r="J41" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -6956,7 +6961,7 @@
       </c>
       <c r="F42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G42" s="0" t="inlineStr">
@@ -6974,7 +6979,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J42" s="0">
+      <c r="J42" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -7006,7 +7011,7 @@
       </c>
       <c r="F43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G43" s="0" t="inlineStr">
@@ -7024,7 +7029,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J43" s="0">
+      <c r="J43" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -7056,7 +7061,7 @@
       </c>
       <c r="F44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G44" s="0" t="inlineStr">
@@ -7074,7 +7079,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J44" s="0">
+      <c r="J44" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -7106,7 +7111,7 @@
       </c>
       <c r="F45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G45" s="0" t="inlineStr">
@@ -7124,7 +7129,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J45" s="0">
+      <c r="J45" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -7156,7 +7161,7 @@
       </c>
       <c r="F46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G46" s="0" t="inlineStr">
@@ -7174,7 +7179,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J46" s="0">
+      <c r="J46" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -7206,7 +7211,7 @@
       </c>
       <c r="F47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G47" s="0" t="inlineStr">
@@ -7224,7 +7229,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J47" s="0">
+      <c r="J47" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -7256,7 +7261,7 @@
       </c>
       <c r="F48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G48" s="0" t="inlineStr">
@@ -7274,7 +7279,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J48" s="0">
+      <c r="J48" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -7306,7 +7311,7 @@
       </c>
       <c r="F49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G49" s="0" t="inlineStr">
@@ -7324,7 +7329,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J49" s="0">
+      <c r="J49" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -7356,7 +7361,7 @@
       </c>
       <c r="F50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G50" s="0" t="inlineStr">
@@ -7374,7 +7379,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J50" s="0">
+      <c r="J50" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -7406,7 +7411,7 @@
       </c>
       <c r="F51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G51" s="0" t="inlineStr">
@@ -7424,7 +7429,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J51" s="0">
+      <c r="J51" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -7456,7 +7461,7 @@
       </c>
       <c r="F52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G52" s="0" t="inlineStr">
@@ -7474,7 +7479,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J52" s="0">
+      <c r="J52" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -7506,7 +7511,7 @@
       </c>
       <c r="F53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G53" s="0" t="inlineStr">
@@ -7524,7 +7529,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J53" s="0">
+      <c r="J53" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -7556,7 +7561,7 @@
       </c>
       <c r="F54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G54" s="0" t="inlineStr">
@@ -7574,7 +7579,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J54" s="0">
+      <c r="J54" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -7606,7 +7611,7 @@
       </c>
       <c r="F55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G55" s="0" t="inlineStr">
@@ -7624,7 +7629,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J55" s="0">
+      <c r="J55" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -7656,7 +7661,7 @@
       </c>
       <c r="F56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G56" s="0" t="inlineStr">
@@ -7674,7 +7679,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J56" s="0">
+      <c r="J56" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -7706,7 +7711,7 @@
       </c>
       <c r="F57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G57" s="0" t="inlineStr">
@@ -7724,7 +7729,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J57" s="0">
+      <c r="J57" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -7756,7 +7761,7 @@
       </c>
       <c r="F58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G58" s="0" t="inlineStr">
@@ -7774,7 +7779,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J58" s="0">
+      <c r="J58" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -7806,7 +7811,7 @@
       </c>
       <c r="F59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G59" s="0" t="inlineStr">
@@ -7824,7 +7829,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J59" s="0">
+      <c r="J59" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -7856,7 +7861,7 @@
       </c>
       <c r="F60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G60" s="0" t="inlineStr">
@@ -7874,7 +7879,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J60" s="0">
+      <c r="J60" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -7906,7 +7911,7 @@
       </c>
       <c r="F61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G61" s="0" t="inlineStr">
@@ -7924,7 +7929,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J61" s="0">
+      <c r="J61" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -7956,7 +7961,7 @@
       </c>
       <c r="F62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G62" s="0" t="inlineStr">
@@ -7974,7 +7979,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J62" s="0">
+      <c r="J62" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -8006,7 +8011,7 @@
       </c>
       <c r="F63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G63" s="0" t="inlineStr">
@@ -8024,7 +8029,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J63" s="0">
+      <c r="J63" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -8056,7 +8061,7 @@
       </c>
       <c r="F64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G64" s="0" t="inlineStr">
@@ -8074,7 +8079,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J64" s="0">
+      <c r="J64" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -8106,7 +8111,7 @@
       </c>
       <c r="F65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G65" s="0" t="inlineStr">
@@ -8124,7 +8129,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J65" s="0">
+      <c r="J65" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -8156,7 +8161,7 @@
       </c>
       <c r="F66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G66" s="0" t="inlineStr">
@@ -8174,7 +8179,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J66" s="0">
+      <c r="J66" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -8206,7 +8211,7 @@
       </c>
       <c r="F67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G67" s="0" t="inlineStr">
@@ -8224,7 +8229,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J67" s="0">
+      <c r="J67" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -8256,7 +8261,7 @@
       </c>
       <c r="F68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G68" s="0" t="inlineStr">
@@ -8274,7 +8279,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J68" s="0">
+      <c r="J68" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -8306,7 +8311,7 @@
       </c>
       <c r="F69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G69" s="0" t="inlineStr">
@@ -8324,7 +8329,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J69" s="0">
+      <c r="J69" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -8356,7 +8361,7 @@
       </c>
       <c r="F70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G70" s="0" t="inlineStr">
@@ -8374,7 +8379,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J70" s="0">
+      <c r="J70" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -8406,7 +8411,7 @@
       </c>
       <c r="F71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G71" s="0" t="inlineStr">
@@ -8424,7 +8429,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J71" s="0">
+      <c r="J71" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -8456,7 +8461,7 @@
       </c>
       <c r="F72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G72" s="0" t="inlineStr">
@@ -8474,7 +8479,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J72" s="0">
+      <c r="J72" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -8506,7 +8511,7 @@
       </c>
       <c r="F73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G73" s="0" t="inlineStr">
@@ -8524,7 +8529,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J73" s="0">
+      <c r="J73" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -8556,7 +8561,7 @@
       </c>
       <c r="F74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G74" s="0" t="inlineStr">
@@ -8574,7 +8579,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J74" s="0">
+      <c r="J74" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -8606,7 +8611,7 @@
       </c>
       <c r="F75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G75" s="0" t="inlineStr">
@@ -8624,7 +8629,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J75" s="0">
+      <c r="J75" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -8656,7 +8661,7 @@
       </c>
       <c r="F76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G76" s="0" t="inlineStr">
@@ -8674,7 +8679,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J76" s="0">
+      <c r="J76" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -8706,7 +8711,7 @@
       </c>
       <c r="F77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G77" s="0" t="inlineStr">
@@ -8724,7 +8729,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J77" s="0">
+      <c r="J77" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -8756,7 +8761,7 @@
       </c>
       <c r="F78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G78" s="0" t="inlineStr">
@@ -8774,7 +8779,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J78" s="0">
+      <c r="J78" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -8806,7 +8811,7 @@
       </c>
       <c r="F79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G79" s="0" t="inlineStr">
@@ -8824,7 +8829,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J79" s="0">
+      <c r="J79" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -8856,7 +8861,7 @@
       </c>
       <c r="F80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G80" s="0" t="inlineStr">
@@ -8874,7 +8879,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J80" s="0">
+      <c r="J80" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -8906,7 +8911,7 @@
       </c>
       <c r="F81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G81" s="0" t="inlineStr">
@@ -8924,7 +8929,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J81" s="0">
+      <c r="J81" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -8956,7 +8961,7 @@
       </c>
       <c r="F82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G82" s="0" t="inlineStr">
@@ -8974,7 +8979,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J82" s="0">
+      <c r="J82" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -9006,7 +9011,7 @@
       </c>
       <c r="F83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G83" s="0" t="inlineStr">
@@ -9024,7 +9029,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J83" s="0">
+      <c r="J83" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -9056,7 +9061,7 @@
       </c>
       <c r="F84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G84" s="0" t="inlineStr">
@@ -9074,7 +9079,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J84" s="0">
+      <c r="J84" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -9106,7 +9111,7 @@
       </c>
       <c r="F85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G85" s="0" t="inlineStr">
@@ -9124,7 +9129,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J85" s="0">
+      <c r="J85" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -9156,7 +9161,7 @@
       </c>
       <c r="F86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G86" s="0" t="inlineStr">
@@ -9174,7 +9179,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J86" s="0">
+      <c r="J86" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -9206,7 +9211,7 @@
       </c>
       <c r="F87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G87" s="0" t="inlineStr">
@@ -9224,7 +9229,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J87" s="0">
+      <c r="J87" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -9256,7 +9261,7 @@
       </c>
       <c r="F88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G88" s="0" t="inlineStr">
@@ -9274,7 +9279,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J88" s="0">
+      <c r="J88" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -9306,7 +9311,7 @@
       </c>
       <c r="F89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G89" s="0" t="inlineStr">
@@ -9324,7 +9329,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J89" s="0">
+      <c r="J89" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -9356,7 +9361,7 @@
       </c>
       <c r="F90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G90" s="0" t="inlineStr">
@@ -9374,7 +9379,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J90" s="0">
+      <c r="J90" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -9406,7 +9411,7 @@
       </c>
       <c r="F91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G91" s="0" t="inlineStr">
@@ -9424,7 +9429,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J91" s="0">
+      <c r="J91" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -9456,7 +9461,7 @@
       </c>
       <c r="F92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G92" s="0" t="inlineStr">
@@ -9474,7 +9479,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J92" s="0">
+      <c r="J92" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -9506,7 +9511,7 @@
       </c>
       <c r="F93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G93" s="0" t="inlineStr">
@@ -9524,7 +9529,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J93" s="0">
+      <c r="J93" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -9556,7 +9561,7 @@
       </c>
       <c r="F94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G94" s="0" t="inlineStr">
@@ -9574,7 +9579,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J94" s="0">
+      <c r="J94" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -9606,7 +9611,7 @@
       </c>
       <c r="F95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G95" s="0" t="inlineStr">
@@ -9624,7 +9629,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J95" s="0">
+      <c r="J95" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -9656,7 +9661,7 @@
       </c>
       <c r="F96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G96" s="0" t="inlineStr">
@@ -9674,7 +9679,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J96" s="0">
+      <c r="J96" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -9706,7 +9711,7 @@
       </c>
       <c r="F97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G97" s="0" t="inlineStr">
@@ -9724,7 +9729,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J97" s="0">
+      <c r="J97" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -9756,7 +9761,7 @@
       </c>
       <c r="F98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G98" s="0" t="inlineStr">
@@ -9774,7 +9779,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J98" s="0">
+      <c r="J98" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -9806,7 +9811,7 @@
       </c>
       <c r="F99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G99" s="0" t="inlineStr">
@@ -9824,7 +9829,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J99" s="0">
+      <c r="J99" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -9856,7 +9861,7 @@
       </c>
       <c r="F100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G100" s="0" t="inlineStr">
@@ -9874,7 +9879,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J100" s="0">
+      <c r="J100" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -9906,7 +9911,7 @@
       </c>
       <c r="F101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G101" s="0" t="inlineStr">
@@ -9924,7 +9929,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J101" s="0">
+      <c r="J101" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -9956,7 +9961,7 @@
       </c>
       <c r="F102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G102" s="0" t="inlineStr">
@@ -9974,7 +9979,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J102" s="0">
+      <c r="J102" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -10006,7 +10011,7 @@
       </c>
       <c r="F103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G103" s="0" t="inlineStr">
@@ -10024,7 +10029,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J103" s="0">
+      <c r="J103" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -10056,7 +10061,7 @@
       </c>
       <c r="F104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G104" s="0" t="inlineStr">
@@ -10074,7 +10079,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J104" s="0">
+      <c r="J104" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -10106,7 +10111,7 @@
       </c>
       <c r="F105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G105" s="0" t="inlineStr">
@@ -10124,7 +10129,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J105" s="0">
+      <c r="J105" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -10156,7 +10161,7 @@
       </c>
       <c r="F106" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G106" s="0" t="inlineStr">
@@ -10174,7 +10179,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J106" s="0">
+      <c r="J106" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -10206,7 +10211,7 @@
       </c>
       <c r="F107" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G107" s="0" t="inlineStr">
@@ -10224,7 +10229,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J107" s="0">
+      <c r="J107" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -10256,7 +10261,7 @@
       </c>
       <c r="F108" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G108" s="0" t="inlineStr">
@@ -10274,7 +10279,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J108" s="0">
+      <c r="J108" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -10306,7 +10311,7 @@
       </c>
       <c r="F109" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G109" s="0" t="inlineStr">
@@ -10324,7 +10329,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J109" s="0">
+      <c r="J109" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -10356,7 +10361,7 @@
       </c>
       <c r="F110" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G110" s="0" t="inlineStr">
@@ -10374,7 +10379,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J110" s="0">
+      <c r="J110" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -10406,7 +10411,7 @@
       </c>
       <c r="F111" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G111" s="0" t="inlineStr">
@@ -10424,7 +10429,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J111" s="0">
+      <c r="J111" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -10456,7 +10461,7 @@
       </c>
       <c r="F112" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G112" s="0" t="inlineStr">
@@ -10474,7 +10479,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J112" s="0">
+      <c r="J112" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -10506,7 +10511,7 @@
       </c>
       <c r="F113" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G113" s="0" t="inlineStr">
@@ -10524,7 +10529,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J113" s="0">
+      <c r="J113" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -10556,7 +10561,7 @@
       </c>
       <c r="F114" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G114" s="0" t="inlineStr">
@@ -10574,7 +10579,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J114" s="0">
+      <c r="J114" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -10606,7 +10611,7 @@
       </c>
       <c r="F115" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G115" s="0" t="inlineStr">
@@ -10624,7 +10629,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J115" s="0">
+      <c r="J115" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -10656,7 +10661,7 @@
       </c>
       <c r="F116" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G116" s="0" t="inlineStr">
@@ -10674,7 +10679,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J116" s="0">
+      <c r="J116" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -10706,7 +10711,7 @@
       </c>
       <c r="F117" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G117" s="0" t="inlineStr">
@@ -10724,7 +10729,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J117" s="0">
+      <c r="J117" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -10756,7 +10761,7 @@
       </c>
       <c r="F118" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G118" s="0" t="inlineStr">
@@ -10774,7 +10779,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J118" s="0">
+      <c r="J118" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -10806,7 +10811,7 @@
       </c>
       <c r="F119" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G119" s="0" t="inlineStr">
@@ -10824,7 +10829,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J119" s="0">
+      <c r="J119" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -10856,7 +10861,7 @@
       </c>
       <c r="F120" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G120" s="0" t="inlineStr">
@@ -10874,7 +10879,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J120" s="0">
+      <c r="J120" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -10906,7 +10911,7 @@
       </c>
       <c r="F121" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G121" s="0" t="inlineStr">
@@ -10924,7 +10929,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J121" s="0">
+      <c r="J121" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -10956,7 +10961,7 @@
       </c>
       <c r="F122" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G122" s="0" t="inlineStr">
@@ -10974,7 +10979,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J122" s="0">
+      <c r="J122" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -11006,7 +11011,7 @@
       </c>
       <c r="F123" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G123" s="0" t="inlineStr">
@@ -11024,7 +11029,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J123" s="0">
+      <c r="J123" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -11056,7 +11061,7 @@
       </c>
       <c r="F124" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G124" s="0" t="inlineStr">
@@ -11074,7 +11079,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J124" s="0">
+      <c r="J124" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -11106,7 +11111,7 @@
       </c>
       <c r="F125" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G125" s="0" t="inlineStr">
@@ -11124,7 +11129,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J125" s="0">
+      <c r="J125" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -11156,7 +11161,7 @@
       </c>
       <c r="F126" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G126" s="0" t="inlineStr">
@@ -11174,7 +11179,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J126" s="0">
+      <c r="J126" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -11206,7 +11211,7 @@
       </c>
       <c r="F127" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G127" s="0" t="inlineStr">
@@ -11224,7 +11229,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J127" s="0">
+      <c r="J127" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -11256,7 +11261,7 @@
       </c>
       <c r="F128" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G128" s="0" t="inlineStr">
@@ -11274,7 +11279,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J128" s="0">
+      <c r="J128" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -11306,7 +11311,7 @@
       </c>
       <c r="F129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G129" s="0" t="inlineStr">
@@ -11324,7 +11329,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J129" s="0">
+      <c r="J129" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -11356,7 +11361,7 @@
       </c>
       <c r="F130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G130" s="0" t="inlineStr">
@@ -11374,7 +11379,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J130" s="0">
+      <c r="J130" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -11406,7 +11411,7 @@
       </c>
       <c r="F131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G131" s="0" t="inlineStr">
@@ -11424,7 +11429,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J131" s="0">
+      <c r="J131" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -11456,7 +11461,7 @@
       </c>
       <c r="F132" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G132" s="0" t="inlineStr">
@@ -11474,7 +11479,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J132" s="0">
+      <c r="J132" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -11506,7 +11511,7 @@
       </c>
       <c r="F133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G133" s="0" t="inlineStr">
@@ -11524,7 +11529,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J133" s="0">
+      <c r="J133" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -11556,7 +11561,7 @@
       </c>
       <c r="F134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G134" s="0" t="inlineStr">
@@ -11574,7 +11579,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J134" s="0">
+      <c r="J134" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -11606,7 +11611,7 @@
       </c>
       <c r="F135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G135" s="0" t="inlineStr">
@@ -11624,7 +11629,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J135" s="0">
+      <c r="J135" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -11656,7 +11661,7 @@
       </c>
       <c r="F136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G136" s="0" t="inlineStr">
@@ -11674,7 +11679,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J136" s="0">
+      <c r="J136" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -11706,7 +11711,7 @@
       </c>
       <c r="F137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G137" s="0" t="inlineStr">
@@ -11724,7 +11729,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J137" s="0">
+      <c r="J137" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -11756,7 +11761,7 @@
       </c>
       <c r="F138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G138" s="0" t="inlineStr">
@@ -11774,7 +11779,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J138" s="0">
+      <c r="J138" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -11806,7 +11811,7 @@
       </c>
       <c r="F139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G139" s="0" t="inlineStr">
@@ -11824,7 +11829,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J139" s="0">
+      <c r="J139" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -11856,7 +11861,7 @@
       </c>
       <c r="F140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G140" s="0" t="inlineStr">
@@ -11874,7 +11879,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J140" s="0">
+      <c r="J140" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -11906,7 +11911,7 @@
       </c>
       <c r="F141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G141" s="0" t="inlineStr">
@@ -11924,7 +11929,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J141" s="0">
+      <c r="J141" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -11956,7 +11961,7 @@
       </c>
       <c r="F142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G142" s="0" t="inlineStr">
@@ -11974,7 +11979,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J142" s="0">
+      <c r="J142" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -12006,7 +12011,7 @@
       </c>
       <c r="F143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G143" s="0" t="inlineStr">
@@ -12024,7 +12029,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J143" s="0">
+      <c r="J143" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -12056,7 +12061,7 @@
       </c>
       <c r="F144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G144" s="0" t="inlineStr">
@@ -12074,7 +12079,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J144" s="0">
+      <c r="J144" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -12106,7 +12111,7 @@
       </c>
       <c r="F145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G145" s="0" t="inlineStr">
@@ -12124,7 +12129,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J145" s="0">
+      <c r="J145" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -12156,7 +12161,7 @@
       </c>
       <c r="F146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G146" s="0" t="inlineStr">
@@ -12174,7 +12179,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J146" s="0">
+      <c r="J146" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -12206,7 +12211,7 @@
       </c>
       <c r="F147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G147" s="0" t="inlineStr">
@@ -12224,7 +12229,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J147" s="0">
+      <c r="J147" s="2">
         <v>8900</v>
       </c>
     </row>
@@ -12256,7 +12261,7 @@
       </c>
       <c r="F148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G148" s="0" t="inlineStr">
@@ -12274,7 +12279,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J148" s="0">
+      <c r="J148" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -12306,7 +12311,7 @@
       </c>
       <c r="F149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G149" s="0" t="inlineStr">
@@ -12324,7 +12329,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J149" s="0">
+      <c r="J149" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -12356,7 +12361,7 @@
       </c>
       <c r="F150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G150" s="0" t="inlineStr">
@@ -12374,7 +12379,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J150" s="0">
+      <c r="J150" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -12406,7 +12411,7 @@
       </c>
       <c r="F151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G151" s="0" t="inlineStr">
@@ -12424,7 +12429,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J151" s="0">
+      <c r="J151" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -12456,7 +12461,7 @@
       </c>
       <c r="F152" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G152" s="0" t="inlineStr">
@@ -12474,7 +12479,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J152" s="0">
+      <c r="J152" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -12506,7 +12511,7 @@
       </c>
       <c r="F153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G153" s="0" t="inlineStr">
@@ -12524,7 +12529,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J153" s="0">
+      <c r="J153" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -12556,7 +12561,7 @@
       </c>
       <c r="F154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G154" s="0" t="inlineStr">
@@ -12574,7 +12579,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J154" s="0">
+      <c r="J154" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -12606,7 +12611,7 @@
       </c>
       <c r="F155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G155" s="0" t="inlineStr">
@@ -12624,7 +12629,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J155" s="0">
+      <c r="J155" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -12656,7 +12661,7 @@
       </c>
       <c r="F156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G156" s="0" t="inlineStr">
@@ -12674,7 +12679,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J156" s="0">
+      <c r="J156" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -12706,7 +12711,7 @@
       </c>
       <c r="F157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G157" s="0" t="inlineStr">
@@ -12724,7 +12729,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J157" s="0">
+      <c r="J157" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -12756,7 +12761,7 @@
       </c>
       <c r="F158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G158" s="0" t="inlineStr">
@@ -12774,7 +12779,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J158" s="0">
+      <c r="J158" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -12806,7 +12811,7 @@
       </c>
       <c r="F159" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G159" s="0" t="inlineStr">
@@ -12824,7 +12829,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J159" s="0">
+      <c r="J159" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -12856,7 +12861,7 @@
       </c>
       <c r="F160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G160" s="0" t="inlineStr">
@@ -12874,7 +12879,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J160" s="0">
+      <c r="J160" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -12906,7 +12911,7 @@
       </c>
       <c r="F161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G161" s="0" t="inlineStr">
@@ -12924,7 +12929,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J161" s="0">
+      <c r="J161" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -12956,7 +12961,7 @@
       </c>
       <c r="F162" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G162" s="0" t="inlineStr">
@@ -12974,7 +12979,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J162" s="0">
+      <c r="J162" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -13006,7 +13011,7 @@
       </c>
       <c r="F163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G163" s="0" t="inlineStr">
@@ -13024,7 +13029,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J163" s="0">
+      <c r="J163" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -13056,7 +13061,7 @@
       </c>
       <c r="F164" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G164" s="0" t="inlineStr">
@@ -13074,7 +13079,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J164" s="0">
+      <c r="J164" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -13106,7 +13111,7 @@
       </c>
       <c r="F165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G165" s="0" t="inlineStr">
@@ -13124,7 +13129,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J165" s="0">
+      <c r="J165" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -13156,7 +13161,7 @@
       </c>
       <c r="F166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G166" s="0" t="inlineStr">
@@ -13174,7 +13179,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J166" s="0">
+      <c r="J166" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -13206,7 +13211,7 @@
       </c>
       <c r="F167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G167" s="0" t="inlineStr">
@@ -13224,7 +13229,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J167" s="0">
+      <c r="J167" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -13256,7 +13261,7 @@
       </c>
       <c r="F168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G168" s="0" t="inlineStr">
@@ -13274,7 +13279,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J168" s="0">
+      <c r="J168" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -13306,7 +13311,7 @@
       </c>
       <c r="F169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G169" s="0" t="inlineStr">
@@ -13324,7 +13329,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J169" s="0">
+      <c r="J169" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -13356,7 +13361,7 @@
       </c>
       <c r="F170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G170" s="0" t="inlineStr">
@@ -13374,7 +13379,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J170" s="0">
+      <c r="J170" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -13406,7 +13411,7 @@
       </c>
       <c r="F171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G171" s="0" t="inlineStr">
@@ -13424,7 +13429,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J171" s="0">
+      <c r="J171" s="2">
         <v>4400</v>
       </c>
     </row>
@@ -13456,7 +13461,7 @@
       </c>
       <c r="F172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G172" s="0" t="inlineStr">
@@ -13474,7 +13479,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J172" s="0">
+      <c r="J172" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -13506,7 +13511,7 @@
       </c>
       <c r="F173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G173" s="0" t="inlineStr">
@@ -13524,7 +13529,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J173" s="0">
+      <c r="J173" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -13556,7 +13561,7 @@
       </c>
       <c r="F174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G174" s="0" t="inlineStr">
@@ -13574,7 +13579,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J174" s="0">
+      <c r="J174" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -13606,7 +13611,7 @@
       </c>
       <c r="F175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G175" s="0" t="inlineStr">
@@ -13624,7 +13629,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J175" s="0">
+      <c r="J175" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -13656,7 +13661,7 @@
       </c>
       <c r="F176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G176" s="0" t="inlineStr">
@@ -13674,7 +13679,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J176" s="0">
+      <c r="J176" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -13706,7 +13711,7 @@
       </c>
       <c r="F177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G177" s="0" t="inlineStr">
@@ -13724,7 +13729,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J177" s="0">
+      <c r="J177" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -13756,7 +13761,7 @@
       </c>
       <c r="F178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G178" s="0" t="inlineStr">
@@ -13774,7 +13779,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J178" s="0">
+      <c r="J178" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -13806,7 +13811,7 @@
       </c>
       <c r="F179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G179" s="0" t="inlineStr">
@@ -13824,7 +13829,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J179" s="0">
+      <c r="J179" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -13856,7 +13861,7 @@
       </c>
       <c r="F180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G180" s="0" t="inlineStr">
@@ -13874,7 +13879,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J180" s="0">
+      <c r="J180" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -13906,7 +13911,7 @@
       </c>
       <c r="F181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G181" s="0" t="inlineStr">
@@ -13924,7 +13929,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J181" s="0">
+      <c r="J181" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -13956,7 +13961,7 @@
       </c>
       <c r="F182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G182" s="0" t="inlineStr">
@@ -13974,7 +13979,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J182" s="0">
+      <c r="J182" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -14006,7 +14011,7 @@
       </c>
       <c r="F183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G183" s="0" t="inlineStr">
@@ -14024,7 +14029,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J183" s="0">
+      <c r="J183" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -14056,7 +14061,7 @@
       </c>
       <c r="F184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G184" s="0" t="inlineStr">
@@ -14074,7 +14079,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J184" s="0">
+      <c r="J184" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -14106,7 +14111,7 @@
       </c>
       <c r="F185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G185" s="0" t="inlineStr">
@@ -14124,7 +14129,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J185" s="0">
+      <c r="J185" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -14156,7 +14161,7 @@
       </c>
       <c r="F186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G186" s="0" t="inlineStr">
@@ -14174,7 +14179,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J186" s="0">
+      <c r="J186" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -14206,7 +14211,7 @@
       </c>
       <c r="F187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G187" s="0" t="inlineStr">
@@ -14224,7 +14229,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J187" s="0">
+      <c r="J187" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -14256,7 +14261,7 @@
       </c>
       <c r="F188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G188" s="0" t="inlineStr">
@@ -14274,7 +14279,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J188" s="0">
+      <c r="J188" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -14306,7 +14311,7 @@
       </c>
       <c r="F189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G189" s="0" t="inlineStr">
@@ -14324,7 +14329,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J189" s="0">
+      <c r="J189" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -14356,7 +14361,7 @@
       </c>
       <c r="F190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G190" s="0" t="inlineStr">
@@ -14374,7 +14379,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J190" s="0">
+      <c r="J190" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -14406,7 +14411,7 @@
       </c>
       <c r="F191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G191" s="0" t="inlineStr">
@@ -14424,7 +14429,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J191" s="0">
+      <c r="J191" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -14456,7 +14461,7 @@
       </c>
       <c r="F192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G192" s="0" t="inlineStr">
@@ -14474,7 +14479,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J192" s="0">
+      <c r="J192" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -14506,7 +14511,7 @@
       </c>
       <c r="F193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G193" s="0" t="inlineStr">
@@ -14524,7 +14529,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J193" s="0">
+      <c r="J193" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -14556,7 +14561,7 @@
       </c>
       <c r="F194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G194" s="0" t="inlineStr">
@@ -14574,7 +14579,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J194" s="0">
+      <c r="J194" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -14606,7 +14611,7 @@
       </c>
       <c r="F195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">24‏/9‏/2026، 1:05 م</t>
+          <t xml:space="preserve">24‏/9‏/2026، 1:11 م</t>
         </is>
       </c>
       <c r="G195" s="0" t="inlineStr">
@@ -14624,7 +14629,7 @@
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="J195" s="0">
+      <c r="J195" s="2">
         <v>14400</v>
       </c>
     </row>
@@ -14657,14 +14662,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">دليل المنتجات وحدود البيع</t>
+          <t xml:space="preserve">دليل المنتجات وحدود البيع · 4</t>
         </is>
       </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"> • 4 سجل</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -14746,7 +14751,7 @@
           <t xml:space="preserve">محلية</t>
         </is>
       </c>
-      <c r="E4" s="0">
+      <c r="E4" s="2">
         <v>5000</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
@@ -14754,16 +14759,16 @@
           <t xml:space="preserve">IQD</t>
         </is>
       </c>
-      <c r="G4" s="0">
+      <c r="G4" s="2">
         <v>4500</v>
       </c>
-      <c r="H4" s="0">
+      <c r="H4" s="2">
         <v>10</v>
       </c>
-      <c r="I4" s="0">
+      <c r="I4" s="2">
         <v>100</v>
       </c>
-      <c r="J4" s="0">
+      <c r="J4" s="2">
         <v>500000</v>
       </c>
       <c r="K4" s="0" t="inlineStr">
@@ -14793,7 +14798,7 @@
           <t xml:space="preserve">محلية</t>
         </is>
       </c>
-      <c r="E5" s="0">
+      <c r="E5" s="2">
         <v>10000</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
@@ -14801,16 +14806,16 @@
           <t xml:space="preserve">IQD</t>
         </is>
       </c>
-      <c r="G5" s="0">
+      <c r="G5" s="2">
         <v>9000</v>
       </c>
-      <c r="H5" s="0">
+      <c r="H5" s="2">
         <v>5</v>
       </c>
-      <c r="I5" s="0">
+      <c r="I5" s="2">
         <v>50</v>
       </c>
-      <c r="J5" s="0">
+      <c r="J5" s="2">
         <v>500000</v>
       </c>
       <c r="K5" s="0" t="inlineStr">
@@ -14840,7 +14845,7 @@
           <t xml:space="preserve">محلية</t>
         </is>
       </c>
-      <c r="E6" s="0">
+      <c r="E6" s="2">
         <v>5000</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
@@ -14848,16 +14853,16 @@
           <t xml:space="preserve">IQD</t>
         </is>
       </c>
-      <c r="G6" s="0">
+      <c r="G6" s="2">
         <v>4500</v>
       </c>
-      <c r="H6" s="0">
+      <c r="H6" s="2">
         <v>10</v>
       </c>
-      <c r="I6" s="0">
+      <c r="I6" s="2">
         <v>100</v>
       </c>
-      <c r="J6" s="0">
+      <c r="J6" s="2">
         <v>500000</v>
       </c>
       <c r="K6" s="0" t="inlineStr">
@@ -14887,7 +14892,7 @@
           <t xml:space="preserve">عالمية</t>
         </is>
       </c>
-      <c r="E7" s="0">
+      <c r="E7" s="2">
         <v>10</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
@@ -14895,16 +14900,16 @@
           <t xml:space="preserve">USD</t>
         </is>
       </c>
-      <c r="G7" s="0">
+      <c r="G7" s="2">
         <v>14500</v>
       </c>
-      <c r="H7" s="0">
+      <c r="H7" s="2">
         <v>3</v>
       </c>
-      <c r="I7" s="0">
+      <c r="I7" s="2">
         <v>30</v>
       </c>
-      <c r="J7" s="0">
+      <c r="J7" s="2">
         <v>500000</v>
       </c>
       <c r="K7" s="0" t="inlineStr">
